--- a/cleaning_pipeline_R/neotree_scripts/zim-scripts/Bindura Hospital Discharge - metadata.xlsx
+++ b/cleaning_pipeline_R/neotree_scripts/zim-scripts/Bindura Hospital Discharge - metadata.xlsx
@@ -893,10 +893,10 @@
         <v>form</v>
       </c>
       <c r="F8" t="str">
-        <v>NeoTreeOutcome</v>
+        <v>NeotreeOutcome</v>
       </c>
       <c r="G8" t="str">
-        <v>Outcome</v>
+        <v>Outcome at discharge</v>
       </c>
       <c r="H8" t="str">
         <v>dropdown</v>
@@ -917,7 +917,7 @@
         <v/>
       </c>
       <c r="N8" t="str">
-        <v>[{"value":"DC","valueLabel":"Discharged"},{"value":"NND","valueLabel":"Died"},{"value":"ABS","valueLabel":"Absconded"},{"value":"STB","valueLabel":"Stillbirth"},{"value":"TRH","valueLabel":"Transferred to other Hospital"},{"value":"TRO","valueLabel":"Transferred to other ward"}]</v>
+        <v>[{"value":"DC","valueLabel":"Discharged"},{"value":"NND","valueLabel":"Died"},{"value":"ABS","valueLabel":"Absconded"},{"value":"STB","valueLabel":"Stillbirth"},{"value":"TRH","valueLabel":"Transferred to other hospital"},{"value":"TRO","valueLabel":"Transferred to other ward"}]</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -1372,7 +1372,7 @@
         <v>AdmReason</v>
       </c>
       <c r="G15" t="str">
-        <v>Presenting Complaint</v>
+        <v>Presenting complaint</v>
       </c>
       <c r="H15" t="str">
         <v>dropdown</v>
@@ -1393,7 +1393,7 @@
         <v/>
       </c>
       <c r="N15" t="str">
-        <v>[{"value":"AD","valueLabel":"Abdominal distension"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"DIB","valueLabel":"Difficulty breathing"},{"value":"DU","valueLabel":"Dumped baby"},{"value":"Fev","valueLabel":"Fever"},{"value":"DF","valueLabel":"Difficulty Feeding"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"BA","valueLabel":"Hypoxic ischaemic encephalopathy"},{"value":"HIVExp","valueLabel":"HIV Exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"LBW","valueLabel":"Low Birth Weight"},{"value":"Apg","valueLabel":"Low Apgars"},{"value":"Mec","valueLabel":"Possible Meconium aspiration"},{"value":"NTD","valueLabel":"Neural tube defect"},{"value":"Prem","valueLabel":"Prematurity"},{"value":"PremRDS","valueLabel":"Prematurity with RDS"},{"value":"SPn","valueLabel":"Pneumonia"},{"value":"OM","valueLabel":"Omphalocele"},{"value":"Cong","valueLabel":"Congenital abnormality"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"NSep","valueLabel":"Suspected neonatal sepsis"},{"value":"O","valueLabel":"Other"}]</v>
+        <v>[{"value":"AD","valueLabel":"Abdominal distension"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"Conv","valueLabel":"Convulsions"},{"value":"DIB","valueLabel":"Respiratory distress / Difficulty breathing/ Fast Breathing"},{"value":"DU","valueLabel":"Dumped baby"},{"value":"Fev","valueLabel":"Fever"},{"value":"DF","valueLabel":"Difficulty Feeding"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"HIE","valueLabel":"Birth Asphyxia / Hypoxic Ischaemic Encephalopathy (HIE)"},{"value":"HIVExp","valueLabel":"HIV Exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"LBW","valueLabel":"Low Birth Weight"},{"value":"Apg","valueLabel":"Low Apgars"},{"value":"Mec","valueLabel":"Possible Meconium aspiration"},{"value":"NTD","valueLabel":"Neural tube defect"},{"value":"Prem","valueLabel":"Premature"},{"value":"PremRDS","valueLabel":"Prematurity with RDS"},{"value":"SPn","valueLabel":"Pneumonia"},{"value":"OM","valueLabel":"Omphalocele"},{"value":"Cong","valueLabel":"Congenital abnormality"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"Risk","valueLabel":"Risk factors for sepsis"},{"value":"NSep","valueLabel":"Sepsis suspected"},{"value":"O","valueLabel":"Other"}]</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -1999,7 +1999,7 @@
         <v>No</v>
       </c>
       <c r="L24" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -2685,7 +2685,7 @@
         <v/>
       </c>
       <c r="N34" t="str">
-        <v>[{"value":"AN","valueLabel":"Anaemia"},{"value":"HIE","valueLabel":"Hypoxic Ischaemic Encephalopathy"},{"value":"BI","valueLabel":"Birth Injury"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BO","valueLabel":"Bowel Obstruction"},{"value":"CHD","valueLabel":"Congenital Heart Disease"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty Feeding"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"HIVXH","valueLabel":"HIV Exposed High Risk"},{"value":"HIVXL","valueLabel":"HIV Exposed Low Risk"},{"value":"JAUN","valueLabel":"Jaundice"},{"value":"LBW","valueLabel":"Low Birth Weight"},{"value":"MA","valueLabel":"Meconium Aspiration"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"MD","valueLabel":"Musculoskeletal Abnormalities"},{"value":"NEC","valueLabel":"Necrotising Enterocolitis"},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)"},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)"},{"value":"NSepNC","valueLabel":"Risk factors for sepsis (but sepsis ruled out)"},{"value":"NB","valueLabel":"Normal baby"},{"value":"OM","valueLabel":"Omphalocele"},{"value":"OCA","valueLabel":"Other congenital abnormality"},{"value":"PR","valueLabel":"Prematurity"},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress"},{"value":"PN","valueLabel":"Pneumonia"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"Twin","valueLabel":"Accompanying Twin"},{"value":"TTN","valueLabel":"Transient Tachypnoea Newborn"},{"value":"OTH","valueLabel":"Other"}]</v>
+        <v>[{"value":"AN","valueLabel":"Anaemia"},{"value":"HIE","valueLabel":"Hypoxic Ischaemic Encephalopathy"},{"value":"BI","valueLabel":"Birth Injury"},{"value":"BBA","valueLabel":"Born before arrival"},{"value":"BO","valueLabel":"Bowel Obstruction"},{"value":"CHD","valueLabel":"Congenital Heart Disease"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"DF","valueLabel":"Difficulty Feeding"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"HIVXH","valueLabel":"HIV Exposed High Risk"},{"value":"HIVXL","valueLabel":"HIV Exposed Low Risk"},{"value":"JAUN","valueLabel":"Jaundice"},{"value":"LBW","valueLabel":"Low Birth Weight"},{"value":"MA","valueLabel":"Meconium Aspiration"},{"value":"HBW","valueLabel":"Macrosomia (&gt;4000g)"},{"value":"MD","valueLabel":"Musculoskeletal Abnormalities"},{"value":"NEC","valueLabel":"Necrotising Enterocolitis"},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)"},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)"},{"value":"NSepNC","valueLabel":"Sepsis (risk factors, but ruled out)"},{"value":"NB","valueLabel":"Normal baby"},{"value":"OM","valueLabel":"Omphalocele"},{"value":"OCA","valueLabel":"Other congenital abnormality"},{"value":"PR","valueLabel":"Prematurity"},{"value":"PremRD","valueLabel":"Premature baby with Respiratory Distress"},{"value":"PN","valueLabel":"Pneumonia"},{"value":"Safe","valueLabel":"Safekeeping"},{"value":"Twin","valueLabel":"Accompanying Twin"},{"value":"TTN","valueLabel":"Transient Tachypnoea Newborn"},{"value":"OTH","valueLabel":"Other"}]</v>
       </c>
       <c r="O34" t="str">
         <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome =  'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO'</v>
@@ -12284,7 +12284,7 @@
         <v>$SPECREV = 'Y'</v>
       </c>
       <c r="N175" t="str">
-        <v>[{"value":"Card","valueLabel":"Cardiologist"},{"value":"Neph","valueLabel":"Nephrology"},{"value":"Ortho","valueLabel":"Orthopaedic Surgery"},{"value":"Surg","valueLabel":"Surgical"},{"value":"Opth","valueLabel":"Opthalmology"},{"value":"MxFx","valueLabel":"Maxillofacial Surgery"},{"value":"Neuro","valueLabel":"Neurology"},{"value":"Endoc","valueLabel":"Endocrinology"}]</v>
+        <v>[{"value":"Card","valueLabel":"Cardiologist"},{"value":"Neph","valueLabel":"Nephrology"},{"value":"Ortho","valueLabel":"Orthopaedic Surgery"},{"value":"Surg","valueLabel":"Surgical"},{"value":"Opth","valueLabel":"Opthalmology"},{"value":"MxFx","valueLabel":"Maxillofacial Surgery"},{"value":"Endoc","valueLabel":"Endocrinology"}]</v>
       </c>
       <c r="O175" t="str">
         <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'ABS'</v>
